--- a/template/6.11/净值.xlsx
+++ b/template/6.11/净值.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -2164,6 +2164,141 @@
         <v>0.99692</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>-0.312%</t>
         </is>
@@ -2181,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -3309,6 +3444,141 @@
         <v>0.99692</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>-0.312%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.99692</v>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>-0.312%</t>
         </is>
@@ -3326,7 +3596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4197,10 +4467,145 @@
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="0" t="n">
         <v>0.99424</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>-2.9148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.99424</v>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>-2.9148%</t>
         </is>
@@ -4218,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5089,10 +5494,145 @@
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="0" t="n">
         <v>0.9959</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>-3.1537%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>-3.1537%</t>
         </is>
@@ -5110,7 +5650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col width="11.5583333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -5169,10 +5709,145 @@
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>1.0001</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5190,7 +5865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col width="12.4416666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -5248,10 +5923,145 @@
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>1.0001</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
